--- a/data/trans_bre/P16A10-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,93</t>
+          <t>-4,81; 1,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,7</t>
+          <t>-3,07; 4,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 3,78</t>
+          <t>-3,41; 3,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,59</t>
+          <t>-4,36; 1,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,94; 66,48</t>
+          <t>-73,3; 52,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 165,91</t>
+          <t>-45,49; 143,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,67; 135,92</t>
+          <t>-56,37; 139,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 44,03</t>
+          <t>-60,34; 55,48</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,54</t>
+          <t>-4,24; 1,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,71</t>
+          <t>-1,43; 3,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,23</t>
+          <t>-4,63; 1,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,82</t>
+          <t>-4,44; 0,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 30,25</t>
+          <t>-52,27; 34,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 133,25</t>
+          <t>-31,35; 145,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 21,91</t>
+          <t>-53,47; 23,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 21,01</t>
+          <t>-54,58; 19,54</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 3,96</t>
+          <t>-2,49; 4,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 4,2</t>
+          <t>-3,91; 4,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -0,01</t>
+          <t>-5,8; 0,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,63</t>
+          <t>-2,38; 3,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,27; 145,41</t>
+          <t>-43,71; 142,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-43,84; 102,06</t>
+          <t>-49,65; 96,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-80,64; 11,9</t>
+          <t>-79,33; 14,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,87; 76,54</t>
+          <t>-28,39; 84,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,25</t>
+          <t>-0,93; 5,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 1,06</t>
+          <t>-6,42; 1,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 8,72</t>
+          <t>0,07; 8,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,74</t>
+          <t>-5,53; 0,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 183,41</t>
+          <t>-21,22; 217,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,71; 25,06</t>
+          <t>-62,94; 25,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 168,12</t>
+          <t>-0,42; 167,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,55; 18,33</t>
+          <t>-66,81; 17,12</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 1,99</t>
+          <t>-7,79; 2,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 4,31</t>
+          <t>-4,78; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 2,75</t>
+          <t>-5,67; 2,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,44</t>
+          <t>-2,05; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,81; 48,42</t>
+          <t>-72,88; 46,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 111,35</t>
+          <t>-57,58; 117,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-75,31; 77,04</t>
+          <t>-71,36; 70,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 161,33</t>
+          <t>-39,34; 150,87</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 4,79</t>
+          <t>-3,81; 4,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 4,68</t>
+          <t>-3,61; 5,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 6,92</t>
+          <t>-1,01; 7,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,92</t>
+          <t>-3,65; 2,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,49; 107,85</t>
+          <t>-46,28; 112,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 116,7</t>
+          <t>-43,98; 115,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 215,0</t>
+          <t>-23,35; 244,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 44,0</t>
+          <t>-48,22; 41,96</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,76</t>
+          <t>-1,64; 3,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; -0,51</t>
+          <t>-5,45; -0,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,6</t>
+          <t>-4,05; 0,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,93</t>
+          <t>-4,29; 1,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 82,49</t>
+          <t>-32,27; 107,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-67,85; -9,25</t>
+          <t>-66,46; -8,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 15,64</t>
+          <t>-60,95; 16,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-62,89; 20,01</t>
+          <t>-67,16; 22,58</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,57</t>
+          <t>-2,48; 2,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,48</t>
+          <t>-1,43; 2,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,89</t>
+          <t>-3,82; 0,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,53</t>
+          <t>-0,98; 4,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 56,19</t>
+          <t>-37,93; 52,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 125,18</t>
+          <t>-37,15; 108,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 16,94</t>
+          <t>-46,77; 19,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 184,85</t>
+          <t>-16,45; 165,34</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,0</t>
+          <t>-1,29; 0,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,57</t>
+          <t>-1,5; 0,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,52</t>
+          <t>-1,72; 0,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,78</t>
+          <t>-1,65; 0,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 20,74</t>
+          <t>-21,61; 18,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 12,51</t>
+          <t>-25,38; 14,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 9,55</t>
+          <t>-26,66; 13,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 15,99</t>
+          <t>-27,51; 16,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A10-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-26,11%</t>
+          <t>-38,71%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,69</t>
+          <t>-5,16; 1,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,54</t>
+          <t>-3,46; 4,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,58</t>
+          <t>-3,52; 3,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,72</t>
+          <t>-5,14; 0,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,3; 52,02</t>
+          <t>-77,32; 43,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,49; 143,97</t>
+          <t>-50,43; 133,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 139,09</t>
+          <t>-61,08; 133,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,34; 55,48</t>
+          <t>-67,08; 12,49</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-26,62%</t>
+          <t>-27,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,68</t>
+          <t>-4,73; 1,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,91</t>
+          <t>-1,67; 3,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 1,34</t>
+          <t>-4,62; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,78</t>
+          <t>-4,6; 0,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,27; 34,7</t>
+          <t>-54,24; 31,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 145,01</t>
+          <t>-34,77; 126,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,47; 23,92</t>
+          <t>-52,9; 35,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,58; 19,54</t>
+          <t>-56,37; 15,7</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 4,17</t>
+          <t>-2,37; 4,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 4,09</t>
+          <t>-4,02; 3,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 0,47</t>
+          <t>-6,0; 0,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,82</t>
+          <t>-2,4; 3,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,71; 142,33</t>
+          <t>-41,64; 148,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,65; 96,51</t>
+          <t>-48,21; 86,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,33; 14,77</t>
+          <t>-83,04; 9,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 84,09</t>
+          <t>-30,21; 80,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,23</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-36,31%</t>
+          <t>-19,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,25</t>
+          <t>-1,09; 4,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,08</t>
+          <t>-6,48; 0,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 8,56</t>
+          <t>-0,44; 8,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,74</t>
+          <t>-3,92; 2,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 217,65</t>
+          <t>-22,75; 179,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,94; 25,5</t>
+          <t>-64,37; 16,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 167,66</t>
+          <t>-7,15; 169,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,81; 17,12</t>
+          <t>-51,4; 52,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 2,13</t>
+          <t>-8,06; 1,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 4,48</t>
+          <t>-5,06; 4,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 2,49</t>
+          <t>-6,39; 2,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,21</t>
+          <t>-1,73; 3,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,88; 46,12</t>
+          <t>-73,63; 35,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,58; 117,92</t>
+          <t>-58,73; 116,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-71,36; 70,73</t>
+          <t>-74,51; 58,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 150,87</t>
+          <t>-36,84; 153,98</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-12,48%</t>
+          <t>-9,26%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 4,83</t>
+          <t>-3,58; 5,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,26</t>
+          <t>-3,93; 4,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 7,38</t>
+          <t>-1,33; 7,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,13</t>
+          <t>-3,41; 2,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,28; 112,13</t>
+          <t>-44,42; 118,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 115,11</t>
+          <t>-46,49; 99,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 244,91</t>
+          <t>-23,11; 253,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,22; 41,96</t>
+          <t>-43,98; 44,79</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-21,99%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,13</t>
+          <t>-1,74; 3,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -0,56</t>
+          <t>-5,63; -0,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,63</t>
+          <t>-4,25; 0,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,18</t>
+          <t>-1,9; 2,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,27; 107,1</t>
+          <t>-33,03; 93,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-66,46; -8,79</t>
+          <t>-67,41; -8,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 16,28</t>
+          <t>-63,39; 18,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-67,16; 22,58</t>
+          <t>-25,79; 57,72</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>-1,23%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,41</t>
+          <t>-2,51; 2,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,39</t>
+          <t>-1,4; 2,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,99</t>
+          <t>-4,0; 0,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,29</t>
+          <t>-2,02; 1,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 52,03</t>
+          <t>-35,71; 48,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 108,56</t>
+          <t>-36,62; 110,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,77; 19,36</t>
+          <t>-50,61; 17,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 165,34</t>
+          <t>-28,16; 41,25</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-8,99%</t>
+          <t>-7,86%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,91</t>
+          <t>-1,29; 0,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,68</t>
+          <t>-1,54; 0,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,71</t>
+          <t>-1,74; 0,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,83</t>
+          <t>-1,37; 0,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 18,91</t>
+          <t>-20,98; 18,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 14,87</t>
+          <t>-26,39; 11,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 13,19</t>
+          <t>-26,7; 9,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 16,97</t>
+          <t>-21,32; 8,7</t>
         </is>
       </c>
     </row>
